--- a/Resultados/IFRS 17/tri_ifrs17_RC daños a cosas.xlsx
+++ b/Resultados/IFRS 17/tri_ifrs17_RC daños a cosas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Python_script\Github\IBNR-NIIF-17\Resultados\IFRS 17\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6126EC-32F1-4771-9FF1-13337594F921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED665CF-3F51-4084-9B8B-08D82CE9AC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -783,40 +783,40 @@
         <v>43101</v>
       </c>
       <c r="G14" s="4">
-        <v>783.09832496605554</v>
+        <v>658.35473428593218</v>
       </c>
       <c r="H14" s="5">
-        <v>967.3085771352296</v>
+        <v>824.17455864793453</v>
       </c>
       <c r="I14" s="5">
-        <v>987.45714050285142</v>
+        <v>840.90265889443765</v>
       </c>
       <c r="J14" s="5">
-        <v>1026.492579966729</v>
+        <v>870.68431131453781</v>
       </c>
       <c r="K14" s="5">
-        <v>1040.920526083097</v>
+        <v>880.83662731798256</v>
       </c>
       <c r="L14" s="5">
-        <v>1050.9423031129511</v>
+        <v>887.56050124498256</v>
       </c>
       <c r="M14" s="5">
-        <v>1057.067979939985</v>
+        <v>891.58037472587228</v>
       </c>
       <c r="N14" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="5">
-        <v>1080.0679173150379</v>
+        <v>905.6656371056182</v>
       </c>
       <c r="P14" s="5">
-        <v>1080.8711128478269</v>
+        <v>906.11940953612975</v>
       </c>
       <c r="Q14" s="5">
-        <v>1081.597447275441</v>
+        <v>906.52678968993837</v>
       </c>
       <c r="R14" s="6">
-        <v>1082.25765208803</v>
+        <v>906.89454038273016</v>
       </c>
     </row>
     <row r="15" spans="6:23" x14ac:dyDescent="0.25">
@@ -824,40 +824,40 @@
         <v>43466</v>
       </c>
       <c r="G15" s="7">
-        <v>639.28815011839686</v>
+        <v>575.46552116973487</v>
       </c>
       <c r="H15" s="8">
-        <v>760.24846942771615</v>
+        <v>675.89135850297691</v>
       </c>
       <c r="I15" s="8">
-        <v>804.5563647182845</v>
+        <v>709.69557219015735</v>
       </c>
       <c r="J15" s="8">
-        <v>801.88994895952237</v>
+        <v>707.81933179106079</v>
       </c>
       <c r="K15" s="8">
-        <v>813.03049648893818</v>
+        <v>715.29381828606074</v>
       </c>
       <c r="L15" s="8">
-        <v>820.85819336887573</v>
+        <v>720.7540197646963</v>
       </c>
       <c r="M15" s="8">
-        <v>825.64276812479306</v>
+        <v>724.01840564738563</v>
       </c>
       <c r="N15" s="15" t="s">
         <v>1</v>
       </c>
       <c r="O15" s="8">
-        <v>843.60730051192911</v>
+        <v>735.45650982777909</v>
       </c>
       <c r="P15" s="8">
-        <v>844.23465144452916</v>
+        <v>735.82500110571539</v>
       </c>
       <c r="Q15" s="8">
-        <v>844.80196856961527</v>
+        <v>736.15581898575635</v>
       </c>
       <c r="R15" s="9">
-        <v>845.31763391880713</v>
+        <v>736.45445529249719</v>
       </c>
     </row>
     <row r="16" spans="6:23" x14ac:dyDescent="0.25">
@@ -865,40 +865,40 @@
         <v>43831</v>
       </c>
       <c r="G16" s="7">
-        <v>636.68419237658918</v>
+        <v>528.59932497988848</v>
       </c>
       <c r="H16" s="8">
-        <v>795.50973975874342</v>
+        <v>649.77350189531967</v>
       </c>
       <c r="I16" s="8">
-        <v>827.19386790433498</v>
+        <v>672.06824008142553</v>
       </c>
       <c r="J16" s="8">
-        <v>833.96204787301167</v>
+        <v>676.60919012342549</v>
       </c>
       <c r="K16" s="8">
-        <v>845.62435211433956</v>
+        <v>684.16473591834927</v>
       </c>
       <c r="L16" s="8">
-        <v>853.76585619226773</v>
+        <v>689.38731328053416</v>
       </c>
       <c r="M16" s="8">
-        <v>858.74224139010198</v>
+        <v>692.50963539247016</v>
       </c>
       <c r="N16" s="15" t="s">
         <v>1</v>
       </c>
       <c r="O16" s="8">
-        <v>877.4269600156789</v>
+        <v>703.44996134794485</v>
       </c>
       <c r="P16" s="8">
-        <v>878.07946103282325</v>
+        <v>703.80241614541751</v>
       </c>
       <c r="Q16" s="8">
-        <v>878.66952152676026</v>
+        <v>704.1188370646945</v>
       </c>
       <c r="R16" s="9">
-        <v>879.20585955922195</v>
+        <v>704.4044769300391</v>
       </c>
     </row>
     <row r="17" spans="6:18" x14ac:dyDescent="0.25">
@@ -906,40 +906,40 @@
         <v>44197</v>
       </c>
       <c r="G17" s="7">
-        <v>779.48073170384362</v>
+        <v>594.69611559647774</v>
       </c>
       <c r="H17" s="8">
-        <v>910.41829791103385</v>
+        <v>686.83116643016683</v>
       </c>
       <c r="I17" s="8">
-        <v>944.04307322647105</v>
+        <v>709.39091300716689</v>
       </c>
       <c r="J17" s="8">
-        <v>959.59105111644169</v>
+        <v>719.74656227179116</v>
       </c>
       <c r="K17" s="8">
-        <v>973.01017829844943</v>
+        <v>727.78381359997888</v>
       </c>
       <c r="L17" s="8">
-        <v>982.37812792605337</v>
+        <v>733.33935756464973</v>
       </c>
       <c r="M17" s="8">
-        <v>988.10416152066261</v>
+        <v>736.66074402994627</v>
       </c>
       <c r="N17" s="15" t="s">
         <v>1</v>
       </c>
       <c r="O17" s="8">
-        <v>1009.6035676764481</v>
+        <v>748.29857294437352</v>
       </c>
       <c r="P17" s="8">
-        <v>1010.354362198205</v>
+        <v>748.6734985772797</v>
       </c>
       <c r="Q17" s="8">
-        <v>1011.033310084435</v>
+        <v>749.01009298392535</v>
       </c>
       <c r="R17" s="9">
-        <v>1011.650442695728</v>
+        <v>749.31394388357387</v>
       </c>
     </row>
     <row r="18" spans="6:18" x14ac:dyDescent="0.25">
@@ -947,40 +947,40 @@
         <v>44562</v>
       </c>
       <c r="G18" s="7">
-        <v>614.77831671778563</v>
+        <v>432.59267071310938</v>
       </c>
       <c r="H18" s="8">
-        <v>708.55640285746904</v>
+        <v>495.51085642410942</v>
       </c>
       <c r="I18" s="8">
-        <v>735.33563036042983</v>
+        <v>512.17306406844966</v>
       </c>
       <c r="J18" s="8">
-        <v>747.44628764588276</v>
+        <v>519.64973809546416</v>
       </c>
       <c r="K18" s="8">
-        <v>757.89873693036736</v>
+        <v>525.45255226176937</v>
       </c>
       <c r="L18" s="8">
-        <v>765.1956361291036</v>
+        <v>529.46359881280375</v>
       </c>
       <c r="M18" s="8">
-        <v>769.65576791987723</v>
+        <v>531.86160624663898</v>
       </c>
       <c r="N18" s="15" t="s">
         <v>1</v>
       </c>
       <c r="O18" s="8">
-        <v>786.40212179535013</v>
+        <v>540.26400101222623</v>
       </c>
       <c r="P18" s="8">
-        <v>786.98693193652309</v>
+        <v>540.5346935270054</v>
       </c>
       <c r="Q18" s="8">
-        <v>787.51577917460145</v>
+        <v>540.77771128412485</v>
       </c>
       <c r="R18" s="9">
-        <v>787.99647715397498</v>
+        <v>540.99708856037626</v>
       </c>
     </row>
     <row r="19" spans="6:18" x14ac:dyDescent="0.25">
@@ -988,40 +988,40 @@
         <v>44927</v>
       </c>
       <c r="G19" s="10">
-        <v>534.07327667766071</v>
+        <v>358.323815174</v>
       </c>
       <c r="H19" s="11">
-        <v>640.58571035683553</v>
+        <v>428.0017156441607</v>
       </c>
       <c r="I19" s="11">
-        <v>664.79604901669552</v>
+        <v>442.39383917836852</v>
       </c>
       <c r="J19" s="11">
-        <v>675.74495014694276</v>
+        <v>448.85187994455401</v>
       </c>
       <c r="K19" s="11">
-        <v>685.19471254111181</v>
+        <v>453.86411002295421</v>
       </c>
       <c r="L19" s="11">
-        <v>691.79163176698341</v>
+        <v>457.32868558797861</v>
       </c>
       <c r="M19" s="11">
-        <v>695.8239101854067</v>
+        <v>459.39998489959351</v>
       </c>
       <c r="N19" s="16" t="s">
         <v>1</v>
       </c>
       <c r="O19" s="11">
-        <v>710.96381288044267</v>
+        <v>466.65762482527219</v>
       </c>
       <c r="P19" s="11">
-        <v>711.49252311183204</v>
+        <v>466.89143778665431</v>
       </c>
       <c r="Q19" s="11">
-        <v>711.97063887270644</v>
+        <v>467.10134644078511</v>
       </c>
       <c r="R19" s="12">
-        <v>712.40522425693587</v>
+        <v>467.29083542854721</v>
       </c>
     </row>
   </sheetData>
